--- a/leetcode刷题路线v3.0.xlsx
+++ b/leetcode刷题路线v3.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\jinbo\LeetCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A568CB-DB55-47A4-B3A3-485318A2E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DCD85A-AEAE-4D25-A69D-668F933D9A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="335">
   <si>
     <r>
       <rPr>
@@ -1816,6 +1816,37 @@
   </si>
   <si>
     <t>不完全对，own数组忘记-'a'</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>做出来了，但是有点绕</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈希函数写错了，没考虑溢出</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2026.8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>对了，但不是最简便做法</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>对了，但不是最简便做法，还可以优化</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2295,14 +2326,17 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2310,49 +2344,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2364,7 +2362,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2382,6 +2392,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2391,20 +2404,38 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2899,17 +2930,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="105" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="30"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="53"/>
       <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:21" s="1" customFormat="1">
@@ -2943,17 +2974,17 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -2974,10 +3005,10 @@
       <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="34"/>
+      <c r="D4" s="42"/>
       <c r="E4" s="12">
         <v>125</v>
       </c>
@@ -3004,7 +3035,7 @@
       <c r="B5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="35"/>
       <c r="E5" s="12">
         <v>344</v>
@@ -3030,7 +3061,7 @@
       <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="35"/>
       <c r="E6" s="12">
         <v>15</v>
@@ -3058,7 +3089,7 @@
       <c r="B7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="35"/>
       <c r="E7" s="12">
         <v>11</v>
@@ -3086,7 +3117,7 @@
       <c r="B8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="31"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>42</v>
@@ -3108,17 +3139,17 @@
       </c>
     </row>
     <row r="9" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -3139,10 +3170,10 @@
       <c r="B10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="37"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="12">
         <v>88</v>
       </c>
@@ -3169,8 +3200,8 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="37"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="12">
         <v>28</v>
       </c>
@@ -3197,8 +3228,8 @@
       <c r="B12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="37"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="12">
         <v>1768</v>
       </c>
@@ -3223,8 +3254,8 @@
       <c r="B13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="37"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="12">
         <v>392</v>
       </c>
@@ -3245,17 +3276,17 @@
       </c>
     </row>
     <row r="14" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -3276,10 +3307,10 @@
       <c r="B15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="12">
         <v>283</v>
       </c>
@@ -3306,7 +3337,7 @@
       <c r="B16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="24"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="35"/>
       <c r="E16" s="12">
         <v>27</v>
@@ -3334,7 +3365,7 @@
       <c r="B17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="24"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="35"/>
       <c r="E17" s="12">
         <v>26</v>
@@ -3362,7 +3393,7 @@
       <c r="B18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="31"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>75</v>
@@ -3384,17 +3415,17 @@
       </c>
     </row>
     <row r="19" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -3415,10 +3446,10 @@
       <c r="B20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="34"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="12">
         <v>1</v>
       </c>
@@ -3445,7 +3476,7 @@
       <c r="B21" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="24"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="35"/>
       <c r="E21" s="12">
         <v>136</v>
@@ -3473,7 +3504,7 @@
       <c r="B22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="24"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="35"/>
       <c r="E22" s="12">
         <v>169</v>
@@ -3501,7 +3532,7 @@
       <c r="B23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="24"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="35"/>
       <c r="E23" s="12">
         <v>49</v>
@@ -3529,7 +3560,7 @@
       <c r="B24" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="24"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="35"/>
       <c r="E24" s="12">
         <v>128</v>
@@ -3555,7 +3586,7 @@
       <c r="B25" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="31"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="36"/>
       <c r="E25" s="12">
         <v>41</v>
@@ -3575,17 +3606,17 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -3606,10 +3637,10 @@
       <c r="B27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="12">
         <v>239</v>
       </c>
@@ -3628,7 +3659,7 @@
       <c r="J27" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="K27" s="56" t="s">
+      <c r="K27" s="20" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3639,7 +3670,7 @@
       <c r="B28" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="24"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="35"/>
       <c r="E28" s="12">
         <v>3</v>
@@ -3659,7 +3690,7 @@
       <c r="J28" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="K28" s="56" t="s">
+      <c r="K28" s="20" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3670,7 +3701,7 @@
       <c r="B29" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="24"/>
+      <c r="C29" s="25"/>
       <c r="D29" s="35"/>
       <c r="E29" s="12">
         <v>438</v>
@@ -3690,7 +3721,7 @@
       <c r="J29" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="K29" s="56" t="s">
+      <c r="K29" s="20" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3701,7 +3732,7 @@
       <c r="B30" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="31"/>
+      <c r="C30" s="26"/>
       <c r="D30" s="36"/>
       <c r="E30" s="12">
         <v>76</v>
@@ -3718,20 +3749,25 @@
       <c r="I30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="31" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -3752,10 +3788,10 @@
       <c r="B32" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="34" t="s">
         <v>71</v>
       </c>
       <c r="E32" s="12">
@@ -3782,8 +3818,8 @@
       <c r="B33" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="44"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="12">
         <v>35</v>
       </c>
@@ -3810,8 +3846,8 @@
       <c r="B34" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="44"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="12">
         <v>69</v>
       </c>
@@ -3838,8 +3874,8 @@
       <c r="B35" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="44"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="37"/>
       <c r="E35" s="12">
         <v>34</v>
       </c>
@@ -3866,8 +3902,8 @@
       <c r="B36" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="45"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="38"/>
       <c r="E36" s="12">
         <v>74</v>
       </c>
@@ -3894,8 +3930,8 @@
       <c r="B37" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="44"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="37"/>
       <c r="E37" s="12">
         <v>33</v>
       </c>
@@ -3922,8 +3958,8 @@
       <c r="B38" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="44"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="12">
         <v>153</v>
       </c>
@@ -3950,8 +3986,8 @@
       <c r="B39" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="46"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="12">
         <v>240</v>
       </c>
@@ -3978,8 +4014,8 @@
       <c r="B40" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="45"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="38"/>
       <c r="E40" s="12">
         <v>4</v>
       </c>
@@ -3998,17 +4034,17 @@
       <c r="J40" s="6"/>
     </row>
     <row r="41" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
@@ -4029,10 +4065,10 @@
       <c r="B42" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="47"/>
+      <c r="D42" s="40"/>
       <c r="E42" s="12">
         <v>560</v>
       </c>
@@ -4048,7 +4084,12 @@
       <c r="I42" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J42" s="6"/>
+      <c r="J42" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="43" spans="1:21" ht="42.75">
       <c r="A43" s="12">
@@ -4057,8 +4098,8 @@
       <c r="B43" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="38"/>
-      <c r="D43" s="47"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="40"/>
       <c r="E43" s="12">
         <v>209</v>
       </c>
@@ -4074,7 +4115,9 @@
       <c r="I43" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="J43" s="6"/>
+      <c r="J43" s="6" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="44" spans="1:21" ht="28.5">
       <c r="A44" s="12">
@@ -4083,8 +4126,8 @@
       <c r="B44" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="48"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="41"/>
       <c r="E44" s="12">
         <v>238</v>
       </c>
@@ -4100,20 +4143,22 @@
       <c r="I44" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J44" s="6"/>
+      <c r="J44" s="6" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="45" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
@@ -4134,10 +4179,10 @@
       <c r="B46" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="42"/>
       <c r="E46" s="12">
         <v>121</v>
       </c>
@@ -4153,7 +4198,9 @@
       <c r="I46" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="J46" s="6"/>
+      <c r="J46" s="6" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="47" spans="1:21" ht="42.95" customHeight="1">
       <c r="A47" s="12">
@@ -4162,7 +4209,7 @@
       <c r="B47" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="24"/>
+      <c r="C47" s="25"/>
       <c r="D47" s="35"/>
       <c r="E47" s="12">
         <v>122</v>
@@ -4179,7 +4226,12 @@
       <c r="I47" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="J47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="48" spans="1:21" ht="42.95" customHeight="1">
       <c r="A48" s="12">
@@ -4188,7 +4240,7 @@
       <c r="B48" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="24"/>
+      <c r="C48" s="25"/>
       <c r="D48" s="35"/>
       <c r="E48" s="12">
         <v>55</v>
@@ -4205,7 +4257,9 @@
       <c r="I48" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="J48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="49" spans="1:21" ht="42.95" customHeight="1">
       <c r="A49" s="12">
@@ -4214,7 +4268,7 @@
       <c r="B49" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="24"/>
+      <c r="C49" s="25"/>
       <c r="D49" s="35"/>
       <c r="E49" s="12">
         <v>45</v>
@@ -4231,7 +4285,12 @@
       <c r="I49" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J49" s="6"/>
+      <c r="J49" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="50" spans="1:21" ht="42.95" customHeight="1">
       <c r="A50" s="12">
@@ -4240,7 +4299,7 @@
       <c r="B50" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="31"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="36"/>
       <c r="E50" s="12">
         <v>763</v>
@@ -4257,20 +4316,22 @@
       <c r="I50" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J50" s="6"/>
+      <c r="J50" s="6" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="51" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
@@ -4291,10 +4352,10 @@
       <c r="B52" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="49"/>
+      <c r="D52" s="43"/>
       <c r="E52" s="17">
         <v>20</v>
       </c>
@@ -4319,8 +4380,8 @@
       <c r="B53" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="50"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="44"/>
       <c r="E53" s="17">
         <v>739</v>
       </c>
@@ -4345,8 +4406,8 @@
       <c r="B54" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="50"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="44"/>
       <c r="E54" s="17">
         <v>239</v>
       </c>
@@ -4371,8 +4432,8 @@
       <c r="B55" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="50"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="44"/>
       <c r="E55" s="17">
         <v>394</v>
       </c>
@@ -4397,8 +4458,8 @@
       <c r="B56" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="50"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="44"/>
       <c r="E56" s="17">
         <v>32</v>
       </c>
@@ -4423,8 +4484,8 @@
       <c r="B57" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="50"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="44"/>
       <c r="E57" s="17">
         <v>84</v>
       </c>
@@ -4449,8 +4510,8 @@
       <c r="B58" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="51"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="45"/>
       <c r="E58" s="17">
         <v>155</v>
       </c>
@@ -4469,17 +4530,17 @@
       <c r="J58" s="6"/>
     </row>
     <row r="59" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="25"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="25"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
@@ -4500,10 +4561,10 @@
       <c r="B60" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D60" s="34"/>
+      <c r="D60" s="42"/>
       <c r="E60" s="12">
         <v>206</v>
       </c>
@@ -4519,7 +4580,9 @@
       <c r="I60" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="J60" s="6"/>
+      <c r="J60" s="6" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="12">
@@ -4528,7 +4591,7 @@
       <c r="B61" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C61" s="24"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="35"/>
       <c r="E61" s="12">
         <v>203</v>
@@ -4552,7 +4615,7 @@
       <c r="B62" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="24"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="35"/>
       <c r="E62" s="12">
         <v>21</v>
@@ -4578,7 +4641,7 @@
       <c r="B63" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="24"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="35"/>
       <c r="E63" s="12">
         <v>2</v>
@@ -4604,7 +4667,7 @@
       <c r="B64" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="24"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="35"/>
       <c r="E64" s="12">
         <v>24</v>
@@ -4630,7 +4693,7 @@
       <c r="B65" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C65" s="24"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="35"/>
       <c r="E65" s="12">
         <v>234</v>
@@ -4656,7 +4719,7 @@
       <c r="B66" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C66" s="24"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="35"/>
       <c r="E66" s="12">
         <v>141</v>
@@ -4682,7 +4745,7 @@
       <c r="B67" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C67" s="24"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="35"/>
       <c r="E67" s="12">
         <v>142</v>
@@ -4708,7 +4771,7 @@
       <c r="B68" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C68" s="24"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="35"/>
       <c r="E68" s="12">
         <v>287</v>
@@ -4734,7 +4797,7 @@
       <c r="B69" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C69" s="24"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="35"/>
       <c r="E69" s="12">
         <v>160</v>
@@ -4760,7 +4823,7 @@
       <c r="B70" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C70" s="24"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="35"/>
       <c r="E70" s="12">
         <v>19</v>
@@ -4786,7 +4849,7 @@
       <c r="B71" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C71" s="24"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="35"/>
       <c r="E71" s="12">
         <v>148</v>
@@ -4812,7 +4875,7 @@
       <c r="B72" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C72" s="24"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="35"/>
       <c r="E72" s="12">
         <v>23</v>
@@ -4838,7 +4901,7 @@
       <c r="B73" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C73" s="24"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="35"/>
       <c r="E73" s="12">
         <v>138</v>
@@ -4864,7 +4927,7 @@
       <c r="B74" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C74" s="24"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="35"/>
       <c r="E74" s="12">
         <v>25</v>
@@ -4884,17 +4947,17 @@
       <c r="J74" s="6"/>
     </row>
     <row r="75" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="25"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="33"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
@@ -4915,10 +4978,10 @@
       <c r="B76" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="D76" s="40"/>
+      <c r="D76" s="29"/>
       <c r="E76" s="12">
         <v>509</v>
       </c>
@@ -4941,8 +5004,8 @@
       <c r="B77" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C77" s="31"/>
-      <c r="D77" s="42"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="31"/>
       <c r="E77" s="12">
         <v>70</v>
       </c>
@@ -4961,17 +5024,17 @@
       <c r="J77" s="6"/>
     </row>
     <row r="78" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="B78" s="25"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
       <c r="L78" s="11"/>
@@ -4992,10 +5055,10 @@
       <c r="B79" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="39" t="s">
+      <c r="C79" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="D79" s="43" t="s">
+      <c r="D79" s="34" t="s">
         <v>166</v>
       </c>
       <c r="E79" s="12">
@@ -5008,7 +5071,7 @@
         <v>1000</v>
       </c>
       <c r="H79" s="12"/>
-      <c r="I79" s="23" t="s">
+      <c r="I79" s="24" t="s">
         <v>168</v>
       </c>
       <c r="J79" s="6"/>
@@ -5020,7 +5083,7 @@
       <c r="B80" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="39"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="35"/>
       <c r="E80" s="12">
         <v>94</v>
@@ -5034,7 +5097,7 @@
       <c r="H80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I80" s="24"/>
+      <c r="I80" s="25"/>
       <c r="J80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="65.099999999999994" customHeight="1">
@@ -5044,7 +5107,7 @@
       <c r="B81" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C81" s="39"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="35"/>
       <c r="E81" s="12">
         <v>145</v>
@@ -5056,7 +5119,7 @@
         <v>1000</v>
       </c>
       <c r="H81" s="12"/>
-      <c r="I81" s="31"/>
+      <c r="I81" s="26"/>
       <c r="J81" s="6"/>
     </row>
     <row r="82" spans="1:21" ht="65.099999999999994" customHeight="1">
@@ -5066,7 +5129,7 @@
       <c r="B82" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C82" s="39"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="36"/>
       <c r="E82" s="12">
         <v>102</v>
@@ -5086,17 +5149,17 @@
       <c r="J82" s="6"/>
     </row>
     <row r="83" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A83" s="25" t="s">
+      <c r="A83" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B83" s="25"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="33"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
       <c r="J83" s="11"/>
       <c r="K83" s="11"/>
       <c r="L83" s="11"/>
@@ -5117,10 +5180,10 @@
       <c r="B84" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="D84" s="40"/>
+      <c r="D84" s="29"/>
       <c r="E84" s="12">
         <v>104</v>
       </c>
@@ -5145,8 +5208,8 @@
       <c r="B85" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="41"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="30"/>
       <c r="E85" s="12">
         <v>226</v>
       </c>
@@ -5171,8 +5234,8 @@
       <c r="B86" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C86" s="24"/>
-      <c r="D86" s="41"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="30"/>
       <c r="E86" s="12">
         <v>101</v>
       </c>
@@ -5197,8 +5260,8 @@
       <c r="B87" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="41"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="30"/>
       <c r="E87" s="12">
         <v>98</v>
       </c>
@@ -5223,8 +5286,8 @@
       <c r="B88" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="24"/>
-      <c r="D88" s="41"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="30"/>
       <c r="E88" s="12">
         <v>108</v>
       </c>
@@ -5249,8 +5312,8 @@
       <c r="B89" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C89" s="24"/>
-      <c r="D89" s="41"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="30"/>
       <c r="E89" s="12">
         <v>230</v>
       </c>
@@ -5275,8 +5338,8 @@
       <c r="B90" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C90" s="24"/>
-      <c r="D90" s="41"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="30"/>
       <c r="E90" s="12">
         <v>112</v>
       </c>
@@ -5301,8 +5364,8 @@
       <c r="B91" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="41"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="30"/>
       <c r="E91" s="12">
         <v>437</v>
       </c>
@@ -5327,8 +5390,8 @@
       <c r="B92" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="41"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="30"/>
       <c r="E92" s="12">
         <v>199</v>
       </c>
@@ -5353,8 +5416,8 @@
       <c r="B93" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C93" s="24"/>
-      <c r="D93" s="41"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="30"/>
       <c r="E93" s="12">
         <v>114</v>
       </c>
@@ -5379,8 +5442,8 @@
       <c r="B94" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C94" s="24"/>
-      <c r="D94" s="41"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="30"/>
       <c r="E94" s="12">
         <v>543</v>
       </c>
@@ -5405,8 +5468,8 @@
       <c r="B95" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C95" s="24"/>
-      <c r="D95" s="41"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="30"/>
       <c r="E95" s="12">
         <v>124</v>
       </c>
@@ -5431,8 +5494,8 @@
       <c r="B96" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C96" s="24"/>
-      <c r="D96" s="41"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="30"/>
       <c r="E96" s="12">
         <v>236</v>
       </c>
@@ -5457,8 +5520,8 @@
       <c r="B97" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C97" s="24"/>
-      <c r="D97" s="41"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="30"/>
       <c r="E97" s="12">
         <v>105</v>
       </c>
@@ -5483,8 +5546,8 @@
       <c r="B98" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C98" s="31"/>
-      <c r="D98" s="42"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="31"/>
       <c r="E98" s="12">
         <v>106</v>
       </c>
@@ -5503,17 +5566,17 @@
       <c r="J98" s="6"/>
     </row>
     <row r="99" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A99" s="25" t="s">
+      <c r="A99" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="B99" s="25"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="25"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="25"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="25"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="33"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="32"/>
       <c r="J99" s="11"/>
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
@@ -5534,10 +5597,10 @@
       <c r="B100" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="D100" s="40"/>
+      <c r="D100" s="29"/>
       <c r="E100" s="12">
         <v>46</v>
       </c>
@@ -5562,8 +5625,8 @@
       <c r="B101" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C101" s="24"/>
-      <c r="D101" s="41"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="30"/>
       <c r="E101" s="12">
         <v>77</v>
       </c>
@@ -5588,8 +5651,8 @@
       <c r="B102" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C102" s="24"/>
-      <c r="D102" s="41"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="30"/>
       <c r="E102" s="12">
         <v>78</v>
       </c>
@@ -5614,8 +5677,8 @@
       <c r="B103" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C103" s="24"/>
-      <c r="D103" s="41"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="30"/>
       <c r="E103" s="12">
         <v>17</v>
       </c>
@@ -5640,8 +5703,8 @@
       <c r="B104" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="24"/>
-      <c r="D104" s="41"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="30"/>
       <c r="E104" s="12">
         <v>22</v>
       </c>
@@ -5666,8 +5729,8 @@
       <c r="B105" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C105" s="24"/>
-      <c r="D105" s="41"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="30"/>
       <c r="E105" s="12">
         <v>39</v>
       </c>
@@ -5692,8 +5755,8 @@
       <c r="B106" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C106" s="24"/>
-      <c r="D106" s="41"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="30"/>
       <c r="E106" s="12">
         <v>131</v>
       </c>
@@ -5718,8 +5781,8 @@
       <c r="B107" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C107" s="31"/>
-      <c r="D107" s="42"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="31"/>
       <c r="E107" s="12">
         <v>51</v>
       </c>
@@ -5738,17 +5801,17 @@
       <c r="J107" s="6"/>
     </row>
     <row r="108" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A108" s="25" t="s">
+      <c r="A108" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="B108" s="25"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="25"/>
-      <c r="E108" s="26"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="33"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+      <c r="I108" s="32"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11"/>
       <c r="L108" s="11"/>
@@ -5769,10 +5832,10 @@
       <c r="B109" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="39" t="s">
+      <c r="C109" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D109" s="40"/>
+      <c r="D109" s="29"/>
       <c r="E109" s="12">
         <v>200</v>
       </c>
@@ -5797,8 +5860,8 @@
       <c r="B110" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="39"/>
-      <c r="D110" s="41"/>
+      <c r="C110" s="27"/>
+      <c r="D110" s="30"/>
       <c r="E110" s="12">
         <v>695</v>
       </c>
@@ -5821,8 +5884,8 @@
       <c r="B111" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C111" s="39"/>
-      <c r="D111" s="42"/>
+      <c r="C111" s="27"/>
+      <c r="D111" s="31"/>
       <c r="E111" s="12">
         <v>79</v>
       </c>
@@ -5841,17 +5904,17 @@
       <c r="J111" s="6"/>
     </row>
     <row r="112" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A112" s="25" t="s">
+      <c r="A112" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="B112" s="25"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="25"/>
-      <c r="E112" s="26"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
-      <c r="I112" s="25"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="32"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="32"/>
+      <c r="G112" s="32"/>
+      <c r="H112" s="32"/>
+      <c r="I112" s="32"/>
       <c r="J112" s="11"/>
       <c r="K112" s="11"/>
       <c r="L112" s="11"/>
@@ -5872,10 +5935,10 @@
       <c r="B113" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C113" s="39" t="s">
+      <c r="C113" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="D113" s="40"/>
+      <c r="D113" s="29"/>
       <c r="E113" s="12">
         <v>200</v>
       </c>
@@ -5900,8 +5963,8 @@
       <c r="B114" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="39"/>
-      <c r="D114" s="41"/>
+      <c r="C114" s="27"/>
+      <c r="D114" s="30"/>
       <c r="E114" s="12">
         <v>695</v>
       </c>
@@ -5924,8 +5987,8 @@
       <c r="B115" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C115" s="39"/>
-      <c r="D115" s="42"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="31"/>
       <c r="E115" s="12">
         <v>994</v>
       </c>
@@ -5944,17 +6007,17 @@
       <c r="J115" s="6"/>
     </row>
     <row r="116" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A116" s="25" t="s">
+      <c r="A116" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="B116" s="25"/>
-      <c r="C116" s="26"/>
-      <c r="D116" s="25"/>
-      <c r="E116" s="26"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="25"/>
-      <c r="H116" s="25"/>
-      <c r="I116" s="25"/>
+      <c r="B116" s="32"/>
+      <c r="C116" s="33"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="33"/>
+      <c r="F116" s="32"/>
+      <c r="G116" s="32"/>
+      <c r="H116" s="32"/>
+      <c r="I116" s="32"/>
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
@@ -5975,10 +6038,10 @@
       <c r="B117" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C117" s="39" t="s">
+      <c r="C117" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="D117" s="40"/>
+      <c r="D117" s="29"/>
       <c r="E117" s="12">
         <v>509</v>
       </c>
@@ -6001,8 +6064,8 @@
       <c r="B118" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C118" s="39"/>
-      <c r="D118" s="41"/>
+      <c r="C118" s="27"/>
+      <c r="D118" s="30"/>
       <c r="E118" s="12">
         <v>70</v>
       </c>
@@ -6027,8 +6090,8 @@
       <c r="B119" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C119" s="39"/>
-      <c r="D119" s="41"/>
+      <c r="C119" s="27"/>
+      <c r="D119" s="30"/>
       <c r="E119" s="12">
         <v>53</v>
       </c>
@@ -6053,8 +6116,8 @@
       <c r="B120" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C120" s="39"/>
-      <c r="D120" s="41"/>
+      <c r="C120" s="27"/>
+      <c r="D120" s="30"/>
       <c r="E120" s="12">
         <v>198</v>
       </c>
@@ -6079,8 +6142,8 @@
       <c r="B121" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C121" s="39"/>
-      <c r="D121" s="41"/>
+      <c r="C121" s="27"/>
+      <c r="D121" s="30"/>
       <c r="E121" s="12">
         <v>152</v>
       </c>
@@ -6105,8 +6168,8 @@
       <c r="B122" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C122" s="39"/>
-      <c r="D122" s="41"/>
+      <c r="C122" s="27"/>
+      <c r="D122" s="30"/>
       <c r="E122" s="12">
         <v>139</v>
       </c>
@@ -6131,8 +6194,8 @@
       <c r="B123" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C123" s="39"/>
-      <c r="D123" s="42"/>
+      <c r="C123" s="27"/>
+      <c r="D123" s="31"/>
       <c r="E123" s="12">
         <v>300</v>
       </c>
@@ -6151,17 +6214,17 @@
       <c r="J123" s="6"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A124" s="25" t="s">
+      <c r="A124" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="B124" s="25"/>
-      <c r="C124" s="26"/>
-      <c r="D124" s="25"/>
-      <c r="E124" s="26"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="25"/>
-      <c r="H124" s="25"/>
-      <c r="I124" s="25"/>
+      <c r="B124" s="32"/>
+      <c r="C124" s="33"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="33"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+      <c r="I124" s="32"/>
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
@@ -6182,10 +6245,10 @@
       <c r="B125" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C125" s="39" t="s">
+      <c r="C125" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="D125" s="40"/>
+      <c r="D125" s="29"/>
       <c r="E125" s="12">
         <v>62</v>
       </c>
@@ -6210,8 +6273,8 @@
       <c r="B126" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C126" s="39"/>
-      <c r="D126" s="41"/>
+      <c r="C126" s="27"/>
+      <c r="D126" s="30"/>
       <c r="E126" s="12">
         <v>63</v>
       </c>
@@ -6236,8 +6299,8 @@
       <c r="B127" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C127" s="39"/>
-      <c r="D127" s="41"/>
+      <c r="C127" s="27"/>
+      <c r="D127" s="30"/>
       <c r="E127" s="12">
         <v>64</v>
       </c>
@@ -6262,8 +6325,8 @@
       <c r="B128" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C128" s="39"/>
-      <c r="D128" s="41"/>
+      <c r="C128" s="27"/>
+      <c r="D128" s="30"/>
       <c r="E128" s="12">
         <v>118</v>
       </c>
@@ -6288,8 +6351,8 @@
       <c r="B129" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C129" s="39"/>
-      <c r="D129" s="41"/>
+      <c r="C129" s="27"/>
+      <c r="D129" s="30"/>
       <c r="E129" s="12">
         <v>72</v>
       </c>
@@ -6314,8 +6377,8 @@
       <c r="B130" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C130" s="39"/>
-      <c r="D130" s="42"/>
+      <c r="C130" s="27"/>
+      <c r="D130" s="31"/>
       <c r="E130" s="12">
         <v>1143</v>
       </c>
@@ -6334,17 +6397,17 @@
       <c r="J130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A131" s="25" t="s">
+      <c r="A131" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="B131" s="25"/>
-      <c r="C131" s="26"/>
-      <c r="D131" s="25"/>
-      <c r="E131" s="26"/>
-      <c r="F131" s="25"/>
-      <c r="G131" s="25"/>
-      <c r="H131" s="25"/>
-      <c r="I131" s="25"/>
+      <c r="B131" s="32"/>
+      <c r="C131" s="33"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="33"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+      <c r="I131" s="32"/>
       <c r="J131" s="11"/>
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
@@ -6365,10 +6428,10 @@
       <c r="B132" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C132" s="39" t="s">
+      <c r="C132" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="D132" s="40"/>
+      <c r="D132" s="29"/>
       <c r="E132" s="12">
         <v>322</v>
       </c>
@@ -6393,8 +6456,8 @@
       <c r="B133" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C133" s="39"/>
-      <c r="D133" s="41"/>
+      <c r="C133" s="27"/>
+      <c r="D133" s="30"/>
       <c r="E133" s="12">
         <v>279</v>
       </c>
@@ -6419,8 +6482,8 @@
       <c r="B134" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="39"/>
-      <c r="D134" s="42"/>
+      <c r="C134" s="27"/>
+      <c r="D134" s="31"/>
       <c r="E134" s="12">
         <v>416</v>
       </c>
@@ -6439,17 +6502,17 @@
       <c r="J134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="14.25">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="B135" s="25"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="25"/>
-      <c r="E135" s="26"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
+      <c r="B135" s="32"/>
+      <c r="C135" s="33"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="33"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
       <c r="L135" s="11"/>
@@ -6470,10 +6533,10 @@
       <c r="B136" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="55" t="s">
+      <c r="C136" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="D136" s="52"/>
+      <c r="D136" s="21"/>
       <c r="E136" s="12">
         <v>73</v>
       </c>
@@ -6498,8 +6561,8 @@
       <c r="B137" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="55"/>
-      <c r="D137" s="53"/>
+      <c r="C137" s="28"/>
+      <c r="D137" s="22"/>
       <c r="E137" s="12">
         <v>48</v>
       </c>
@@ -6524,8 +6587,8 @@
       <c r="B138" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C138" s="55"/>
-      <c r="D138" s="53"/>
+      <c r="C138" s="28"/>
+      <c r="D138" s="22"/>
       <c r="E138" s="12">
         <v>54</v>
       </c>
@@ -6550,8 +6613,8 @@
       <c r="B139" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C139" s="55"/>
-      <c r="D139" s="53"/>
+      <c r="C139" s="28"/>
+      <c r="D139" s="22"/>
       <c r="E139" s="12">
         <v>189</v>
       </c>
@@ -6576,8 +6639,8 @@
       <c r="B140" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C140" s="55"/>
-      <c r="D140" s="53"/>
+      <c r="C140" s="28"/>
+      <c r="D140" s="22"/>
       <c r="E140" s="12">
         <v>56</v>
       </c>
@@ -6602,8 +6665,8 @@
       <c r="B141" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C141" s="55"/>
-      <c r="D141" s="53"/>
+      <c r="C141" s="28"/>
+      <c r="D141" s="22"/>
       <c r="E141" s="12">
         <v>31</v>
       </c>
@@ -6628,8 +6691,8 @@
       <c r="B142" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="55"/>
-      <c r="D142" s="53"/>
+      <c r="C142" s="28"/>
+      <c r="D142" s="22"/>
       <c r="E142" s="12">
         <v>207</v>
       </c>
@@ -6654,8 +6717,8 @@
       <c r="B143" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C143" s="55"/>
-      <c r="D143" s="53"/>
+      <c r="C143" s="28"/>
+      <c r="D143" s="22"/>
       <c r="E143" s="12">
         <v>215</v>
       </c>
@@ -6680,8 +6743,8 @@
       <c r="B144" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C144" s="55"/>
-      <c r="D144" s="53"/>
+      <c r="C144" s="28"/>
+      <c r="D144" s="22"/>
       <c r="E144" s="12">
         <v>347</v>
       </c>
@@ -6706,8 +6769,8 @@
       <c r="B145" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C145" s="55"/>
-      <c r="D145" s="53"/>
+      <c r="C145" s="28"/>
+      <c r="D145" s="22"/>
       <c r="E145" s="12">
         <v>295</v>
       </c>
@@ -6732,8 +6795,8 @@
       <c r="B146" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C146" s="55"/>
-      <c r="D146" s="53"/>
+      <c r="C146" s="28"/>
+      <c r="D146" s="22"/>
       <c r="E146" s="12">
         <v>208</v>
       </c>
@@ -6758,8 +6821,8 @@
       <c r="B147" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C147" s="55"/>
-      <c r="D147" s="53"/>
+      <c r="C147" s="28"/>
+      <c r="D147" s="22"/>
       <c r="E147" s="12">
         <v>146</v>
       </c>
@@ -6784,8 +6847,8 @@
       <c r="B148" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="C148" s="55"/>
-      <c r="D148" s="53"/>
+      <c r="C148" s="28"/>
+      <c r="D148" s="22"/>
       <c r="E148" s="12">
         <v>5</v>
       </c>
@@ -6810,8 +6873,8 @@
       <c r="B149" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="C149" s="55"/>
-      <c r="D149" s="54"/>
+      <c r="C149" s="28"/>
+      <c r="D149" s="23"/>
       <c r="E149" s="12">
         <v>28</v>
       </c>
@@ -6831,6 +6894,52 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="C52:C58"/>
+    <mergeCell ref="C60:C74"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="C32:C40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D132:D134"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D79:D82"/>
+    <mergeCell ref="D84:D98"/>
+    <mergeCell ref="D32:D40"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D50"/>
+    <mergeCell ref="D52:D58"/>
+    <mergeCell ref="D60:D74"/>
+    <mergeCell ref="D20:D25"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C79:C82"/>
+    <mergeCell ref="C84:C98"/>
+    <mergeCell ref="C100:C107"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A99:I99"/>
     <mergeCell ref="D136:D149"/>
     <mergeCell ref="I79:I81"/>
     <mergeCell ref="C132:C134"/>
@@ -6847,52 +6956,6 @@
     <mergeCell ref="A116:I116"/>
     <mergeCell ref="A124:I124"/>
     <mergeCell ref="A131:I131"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="C79:C82"/>
-    <mergeCell ref="C84:C98"/>
-    <mergeCell ref="C100:C107"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="A108:I108"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="D132:D134"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D79:D82"/>
-    <mergeCell ref="D84:D98"/>
-    <mergeCell ref="D32:D40"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D50"/>
-    <mergeCell ref="D52:D58"/>
-    <mergeCell ref="D60:D74"/>
-    <mergeCell ref="D20:D25"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="C32:C40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="C52:C58"/>
-    <mergeCell ref="C60:C74"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A31:I31"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
